--- a/artfynd/A 61551-2025 artfynd.xlsx
+++ b/artfynd/A 61551-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130818478</v>
       </c>
       <c r="B2" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130818435</v>
       </c>
       <c r="B3" t="n">
-        <v>91733</v>
+        <v>91734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130818494</v>
       </c>
       <c r="B4" t="n">
-        <v>57809</v>
+        <v>57810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130818461</v>
       </c>
       <c r="B5" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61551-2025 artfynd.xlsx
+++ b/artfynd/A 61551-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>130818435</v>
       </c>
       <c r="B3" t="n">
-        <v>91734</v>
+        <v>91742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61551-2025 artfynd.xlsx
+++ b/artfynd/A 61551-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130818478</v>
+        <v>130818377</v>
       </c>
       <c r="B2" t="n">
-        <v>58256</v>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>5445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575936</v>
+        <v>575972</v>
       </c>
       <c r="R2" t="n">
-        <v>6394769</v>
+        <v>6394794</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130818435</v>
+        <v>130818408</v>
       </c>
       <c r="B3" t="n">
-        <v>91767</v>
+        <v>91867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -822,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575949</v>
+        <v>575964</v>
       </c>
       <c r="R3" t="n">
-        <v>6394778</v>
+        <v>6394792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Klen ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130818494</v>
+        <v>130818435</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>91867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575936</v>
+        <v>575949</v>
       </c>
       <c r="R4" t="n">
-        <v>6394769</v>
+        <v>6394778</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lågt mot S</t>
+          <t>Klen ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130818461</v>
+        <v>130818523</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,49 +1018,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 61551, Marielund, Sm</t>
+          <t>A 61551, Maielund, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575936</v>
+        <v>575928</v>
       </c>
       <c r="R5" t="n">
-        <v>6394769</v>
+        <v>6394697</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,6 +1097,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,6 +1113,443 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130818494</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 61551, Marielund, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575936</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6394769</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lågt mot S</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130818478</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 61551, Marielund, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575936</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6394769</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130818354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 61551, Marielund, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575978</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6394769</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130818461</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 61551, Marielund, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575936</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6394769</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
